--- a/diseases/d168/2000-2004.xlsx
+++ b/diseases/d168/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9020,7 +9020,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14460,7 +14460,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15548,7 +15548,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16092,7 +16092,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17180,7 +17180,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18268,7 +18268,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19356,7 +19356,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19900,7 +19900,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20444,7 +20444,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21532,7 +21532,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22076,7 +22076,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -23164,7 +23164,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -23708,7 +23708,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -24252,7 +24252,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -24796,7 +24796,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -25340,7 +25340,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -25884,7 +25884,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26428,7 +26428,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -26972,7 +26972,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -27516,7 +27516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -28604,7 +28604,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -29148,7 +29148,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -29692,7 +29692,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -30236,7 +30236,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -30780,7 +30780,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -31324,7 +31324,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">

--- a/diseases/d168/2000-2004.xlsx
+++ b/diseases/d168/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9020,7 +9020,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14460,7 +14460,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15548,7 +15548,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16092,7 +16092,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17180,7 +17180,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18268,7 +18268,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19356,7 +19356,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19900,7 +19900,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20444,7 +20444,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21532,7 +21532,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22076,7 +22076,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -23164,7 +23164,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -23708,7 +23708,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -24252,7 +24252,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -24796,7 +24796,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -25340,7 +25340,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -25884,7 +25884,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26428,7 +26428,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -26972,7 +26972,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -27516,7 +27516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -28604,7 +28604,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -29148,7 +29148,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -29692,7 +29692,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -30236,7 +30236,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -30780,7 +30780,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -31324,7 +31324,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">

--- a/diseases/d168/2000-2004.xlsx
+++ b/diseases/d168/2000-2004.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -6061,9 +6019,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -6457,9 +6412,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -6605,9 +6557,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -7001,9 +6950,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -7149,9 +7095,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -7545,9 +7488,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -7693,9 +7633,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -8089,9 +8026,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -8237,9 +8171,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -8633,9 +8564,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -8781,9 +8709,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -9177,9 +9102,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -9325,9 +9247,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -9721,9 +9640,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -9869,9 +9785,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -10265,9 +10178,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -10413,9 +10323,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -10809,9 +10716,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -10957,9 +10861,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -11353,9 +11254,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -11501,9 +11399,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -11897,9 +11792,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -12045,9 +11937,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -12441,9 +12330,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -12589,9 +12475,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -12985,9 +12868,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -13133,9 +13013,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -13529,9 +13406,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -13677,9 +13551,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -14073,9 +13944,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -14221,9 +14089,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -14617,9 +14482,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -14765,9 +14627,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -15161,9 +15020,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -15309,9 +15165,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -15705,9 +15558,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -15853,9 +15703,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -16249,9 +16096,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -16397,9 +16241,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -16793,9 +16634,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -16941,9 +16779,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -17337,9 +17172,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -17485,9 +17317,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -17881,9 +17710,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -18029,9 +17855,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -18425,9 +18248,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -18573,9 +18393,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -18969,9 +18786,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -19117,9 +18931,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -19513,9 +19324,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -19661,9 +19469,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -20057,9 +19862,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -20205,9 +20007,6 @@
       <c r="O107" t="n">
         <v>1</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.005045547545216242</v>
       </c>
@@ -20601,9 +20400,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -20749,9 +20545,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -21145,9 +20938,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -21293,9 +21083,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -21689,9 +21476,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -21837,9 +21621,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -22233,9 +22014,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -22381,9 +22159,6 @@
       <c r="O119" t="n">
         <v>1</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.005045547545216242</v>
       </c>
@@ -22777,9 +22552,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -22925,9 +22697,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -23321,9 +23090,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -23469,9 +23235,6 @@
       <c r="O125" t="n">
         <v>1</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.005045547545216242</v>
       </c>
@@ -23865,9 +23628,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -24013,9 +23773,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -24409,9 +24166,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -24557,9 +24311,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -24953,9 +24704,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -25101,9 +24849,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -25497,9 +25242,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -25645,9 +25387,6 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
@@ -26041,9 +25780,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -26189,9 +25925,6 @@
       <c r="O140" t="n">
         <v>1</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.004988357920866386</v>
       </c>
@@ -26585,9 +26318,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -26733,9 +26463,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -27129,9 +26856,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
@@ -27277,9 +27001,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -27673,9 +27394,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -27821,9 +27539,6 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -28217,9 +27932,6 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
@@ -28365,9 +28077,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -28761,9 +28470,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -28909,9 +28615,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -29305,9 +29008,6 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
@@ -29453,9 +29153,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -29849,9 +29546,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -29997,9 +29691,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -30393,9 +30084,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -30541,9 +30229,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -30937,9 +30622,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -31085,9 +30767,6 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -31479,9 +31158,6 @@
         <v>0</v>
       </c>
       <c r="O169" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q169" t="n">
         <v>0</v>
       </c>
       <c r="R169" t="n">

--- a/diseases/d168/2000-2004.xlsx
+++ b/diseases/d168/2000-2004.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -13259,7 +13259,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -13797,7 +13797,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -14873,7 +14873,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -15949,7 +15949,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -16487,7 +16487,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -17025,7 +17025,7 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN90" t="b">
@@ -17563,7 +17563,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -18101,7 +18101,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -18639,7 +18639,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -19177,7 +19177,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -19715,7 +19715,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -20253,7 +20253,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -20791,7 +20791,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -21867,7 +21867,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -22405,7 +22405,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -22943,7 +22943,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -23481,7 +23481,7 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN126" t="b">
@@ -24019,7 +24019,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -24557,7 +24557,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -25095,7 +25095,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -25633,7 +25633,7 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN138" t="b">
@@ -26171,7 +26171,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -26709,7 +26709,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -27247,7 +27247,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -27785,7 +27785,7 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN150" t="b">
@@ -28323,7 +28323,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -28861,7 +28861,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -29399,7 +29399,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -29937,7 +29937,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN162" t="b">
@@ -30475,7 +30475,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -31013,7 +31013,7 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN168" t="b">

--- a/diseases/d168/2000-2004.xlsx
+++ b/diseases/d168/2000-2004.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14863,7 +14863,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15939,7 +15939,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16477,7 +16477,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17015,7 +17015,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18091,7 +18091,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19167,7 +19167,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19705,7 +19705,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20243,7 +20243,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -20781,7 +20781,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21319,7 +21319,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -21857,7 +21857,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -22395,7 +22395,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -22933,7 +22933,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -24009,7 +24009,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -24547,7 +24547,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -25085,7 +25085,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -25623,7 +25623,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26161,7 +26161,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -26699,7 +26699,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -27237,7 +27237,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -27775,7 +27775,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -28313,7 +28313,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -28851,7 +28851,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -29927,7 +29927,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -30465,7 +30465,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -31003,7 +31003,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">

--- a/diseases/d168/2000-2004.xlsx
+++ b/diseases/d168/2000-2004.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14863,7 +14863,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15939,7 +15939,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16477,7 +16477,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17015,7 +17015,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18091,7 +18091,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19167,7 +19167,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19705,7 +19705,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20243,7 +20243,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -20781,7 +20781,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21319,7 +21319,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -21857,7 +21857,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -22395,7 +22395,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -22933,7 +22933,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -24009,7 +24009,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -24547,7 +24547,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -25085,7 +25085,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -25623,7 +25623,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26161,7 +26161,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -26699,7 +26699,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -27237,7 +27237,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -27775,7 +27775,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -28313,7 +28313,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -28851,7 +28851,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -29927,7 +29927,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -30465,7 +30465,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -31003,7 +31003,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">

--- a/diseases/d168/2000-2004.xlsx
+++ b/diseases/d168/2000-2004.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14863,7 +14863,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15939,7 +15939,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16477,7 +16477,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17015,7 +17015,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18091,7 +18091,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19167,7 +19167,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19705,7 +19705,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20243,7 +20243,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -20781,7 +20781,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21319,7 +21319,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -21857,7 +21857,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -22395,7 +22395,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -22933,7 +22933,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -24009,7 +24009,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -24547,7 +24547,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -25085,7 +25085,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -25623,7 +25623,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26161,7 +26161,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -26699,7 +26699,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -27237,7 +27237,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -27775,7 +27775,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -28313,7 +28313,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -28851,7 +28851,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -29927,7 +29927,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -30465,7 +30465,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -31003,7 +31003,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
